--- a/2026_sales.xlsx
+++ b/2026_sales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/livharris/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C48256-4F99-484D-8E8C-05E7885EE3EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563B22FB-86C8-284F-9EED-C4707A1731A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16120" xr2:uid="{26456327-F351-0244-8010-5EEB21DA48A5}"/>
+    <workbookView xWindow="13400" yWindow="600" windowWidth="15020" windowHeight="16100" xr2:uid="{26456327-F351-0244-8010-5EEB21DA48A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>391686.17</v>
+        <v>408360.57</v>
       </c>
     </row>
   </sheetData>

--- a/2026_sales.xlsx
+++ b/2026_sales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/livharris/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563B22FB-86C8-284F-9EED-C4707A1731A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5775E3CF-B087-C34C-BCDC-72ED0B5BF3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13400" yWindow="600" windowWidth="15020" windowHeight="16100" xr2:uid="{26456327-F351-0244-8010-5EEB21DA48A5}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="17200" windowHeight="16120" xr2:uid="{26456327-F351-0244-8010-5EEB21DA48A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="1">
-        <v>408360.57</v>
+        <v>437157.15</v>
       </c>
     </row>
   </sheetData>
